--- a/frontend/assets/templates/维保计划-强电-modified.xlsx
+++ b/frontend/assets/templates/维保计划-强电-modified.xlsx
@@ -461,7 +461,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -872,6 +872,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <diagonalUp val="1"/>
+      <vertical/>
+      <horizontal/>
+    </border>
+    <border>
+      <diagonalDown val="1"/>
+      <vertical/>
+      <horizontal/>
+    </border>
   </borders>
   <cellStyleXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -936,7 +946,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1167,6 +1177,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0"/>
   </cellXfs>
   <cellStyles count="31">
     <cellStyle name="Normal_Book1" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>

--- a/frontend/assets/templates/维保计划-强电-modified.xlsx
+++ b/frontend/assets/templates/维保计划-强电-modified.xlsx
@@ -873,14 +873,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonalUp val="1"/>
-      <vertical/>
-      <horizontal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonalDown val="1"/>
-      <vertical/>
-      <horizontal/>
     </border>
   </borders>
   <cellStyleXfs count="31">

--- a/frontend/assets/templates/维保计划-强电-modified.xlsx
+++ b/frontend/assets/templates/维保计划-强电-modified.xlsx
@@ -420,7 +420,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,21 +445,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="1F497D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B050"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -873,29 +858,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonalUp val="1"/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonalDown val="1"/>
     </border>
   </borders>
@@ -962,7 +927,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1190,11 +1155,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="12"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="12"/>
   </cellXfs>
   <cellStyles count="31">
     <cellStyle name="Normal_Book1" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>

--- a/frontend/assets/templates/维保计划-强电-modified.xlsx
+++ b/frontend/assets/templates/维保计划-强电-modified.xlsx
@@ -420,7 +420,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,6 +445,21 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -859,9 +874,13 @@
     </border>
     <border>
       <diagonalUp val="1"/>
+      <vertical/>
+      <horizontal/>
     </border>
     <border>
       <diagonalDown val="1"/>
+      <vertical/>
+      <horizontal/>
     </border>
   </borders>
   <cellStyleXfs count="31">
@@ -927,7 +946,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1155,8 +1174,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="12"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="12"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="31">
     <cellStyle name="Normal_Book1" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
